--- a/main/ig/StructureDefinition-fr-diagnostic-report-bio-chapter-document.xlsx
+++ b/main/ig/StructureDefinition-fr-diagnostic-report-bio-chapter-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T08:08:15+00:00</t>
+    <t>2026-05-18T14:11:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-diagnostic-report-bio-chapter-document.xlsx
+++ b/main/ig/StructureDefinition-fr-diagnostic-report-bio-chapter-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T14:11:29+00:00</t>
+    <t>2026-05-21T09:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-diagnostic-report-bio-chapter-document.xlsx
+++ b/main/ig/StructureDefinition-fr-diagnostic-report-bio-chapter-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T09:18:21+00:00</t>
+    <t>2026-06-01T14:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-diagnostic-report-bio-chapter-document.xlsx
+++ b/main/ig/StructureDefinition-fr-diagnostic-report-bio-chapter-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:41:15+00:00</t>
+    <t>2026-06-01T15:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-diagnostic-report-bio-chapter-document.xlsx
+++ b/main/ig/StructureDefinition-fr-diagnostic-report-bio-chapter-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T15:18:33+00:00</t>
+    <t>2026-06-02T07:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-diagnostic-report-bio-chapter-document.xlsx
+++ b/main/ig/StructureDefinition-fr-diagnostic-report-bio-chapter-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$61</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2158" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2229" uniqueCount="425">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T07:35:19+00:00</t>
+    <t>2026-06-04T15:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/DiagnosticReport</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-diagnostic-report-document</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -486,7 +486,7 @@
 </t>
   </si>
   <si>
-    <t>Business identifier for report</t>
+    <t>Identifiant</t>
   </si>
   <si>
     <t>Identifiers assigned to this report by the performer or other systems.</t>
@@ -554,6 +554,9 @@
     <t>Diagnostic services routinely issue provisional/incomplete reports, and sometimes withdraw previously released reports.</t>
   </si>
   <si>
+    <t>final</t>
+  </si>
+  <si>
     <t>required</t>
   </si>
   <si>
@@ -583,7 +586,7 @@
 </t>
   </si>
   <si>
-    <t>Codes des chapitres de CR BIO</t>
+    <t>Catégorie du rapport de biologie</t>
   </si>
   <si>
     <t>A code that classifies the clinical discipline, department or diagnostic service that created the report (e.g. cardiology, biochemistry, hematology, MRI). This is used for searching, sorting and display purposes.</t>
@@ -592,13 +595,23 @@
     <t>Multiple categories are allowed using various categorization schemes.   The level of granularity is defined by the category concepts in the value set. More fine-grained filtering can be performed using the metadata and/or terminology hierarchy in DiagnosticReport.code.</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes for diagnostic service sections.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="26436-6"/&gt;
+    &lt;display value="Biologie polyvalente"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-resultat-type-cisis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:$this}
+</t>
+  </si>
+  <si>
+    <t>open</t>
   </si>
   <si>
     <t>OBR-24</t>
@@ -608,6 +621,18 @@
   </si>
   <si>
     <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:chapitreBIO</t>
+  </si>
+  <si>
+    <t>chapitreBIO</t>
+  </si>
+  <si>
+    <t>Codes des chapitres du compte-rendu de BIO</t>
+  </si>
+  <si>
+    <t>Le code du chapitre doit être un code issu du jeu de valeurs Circuit de la biologie (disponible sur bioloinc.fr), onglet ‘2.Chapitres LOINC’ et contenant les codes et libellés traduits en français pour la biologie.</t>
   </si>
   <si>
     <t>DiagnosticReport.code</t>
@@ -715,8 +740,8 @@
 Effective TimeOccurrence</t>
   </si>
   <si>
-    <t>dateTime
-Period</t>
+    <t xml:space="preserve">dateTime
+</t>
   </si>
   <si>
     <t>Date et heure de création du document</t>
@@ -782,11 +807,11 @@
 ServicePractitionerDepartmentCompanyAuthorized byDirector</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitioner-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-organization-document)
 </t>
   </si>
   <si>
-    <t>Responsible Diagnostic Service</t>
+    <t>Exécutant</t>
   </si>
   <si>
     <t>The diagnostic service that is responsible for issuing the report.</t>
@@ -798,6 +823,10 @@
     <t>Need to know whom to contact if there are queries about the results. Also may need to track the source of reports for secondary data analysis.</t>
   </si>
   <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -810,7 +839,39 @@
     <t>FiveWs.actor</t>
   </si>
   <si>
-    <t>DiagnosticReport.performer.id</t>
+    <t>DiagnosticReport.performer:organization</t>
+  </si>
+  <si>
+    <t>organization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-organization-document)
+</t>
+  </si>
+  <si>
+    <t>Organization productrice du CR de biologie</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter</t>
+  </si>
+  <si>
+    <t>Analyzed by
+Reported by</t>
+  </si>
+  <si>
+    <t>Interpréteur de résultat primaire</t>
+  </si>
+  <si>
+    <t>The practitioner or organization that is responsible for the report's conclusions and interpretations.</t>
+  </si>
+  <si>
+    <t>Might not be the same entity that takes responsibility for the clinical report.</t>
+  </si>
+  <si>
+    <t>OBR-32, PRT-8 (where this PRT-4-Participation = "PI")</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.id</t>
   </si>
   <si>
     <t xml:space="preserve">string
@@ -829,7 +890,7 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>DiagnosticReport.performer.extension</t>
+    <t>DiagnosticReport.resultsInterpreter.extension</t>
   </si>
   <si>
     <t>Extension</t>
@@ -845,13 +906,10 @@
     <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Element.extension</t>
   </si>
   <si>
-    <t>DiagnosticReport.performer.extension:author</t>
+    <t>DiagnosticReport.resultsInterpreter.extension:author</t>
   </si>
   <si>
     <t>author</t>
@@ -861,49 +919,49 @@
 </t>
   </si>
   <si>
-    <t>Auteur du compte-rendu de BIO (Médecin - Biologie médicale)</t>
+    <t>Auteur du compte-rendu (Médecin - Radiologue - Biologiste ...)</t>
   </si>
   <si>
     <t>Extension permettant de représenter un acteur impliqué dans le document avec son type et sa référence.</t>
   </si>
   <si>
-    <t>DiagnosticReport.performer.extension:author.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension:author.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension.extension</t>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension.extension</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>DiagnosticReport.performer.extension:author.extension:type</t>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:type</t>
   </si>
   <si>
     <t>type</t>
   </si>
   <si>
-    <t>DiagnosticReport.performer.extension:author.extension:type.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension.extension.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension:author.extension:type.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension.extension.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension:author.extension:type.url</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension.extension.url</t>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:type.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension.extension.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:type.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:type.url</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension.extension.url</t>
   </si>
   <si>
     <t>identifies the meaning of the extension</t>
@@ -918,10 +976,10 @@
     <t>Extension.url</t>
   </si>
   <si>
-    <t>DiagnosticReport.performer.extension:author.extension:type.value[x]</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension.extension.value[x]</t>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:type.value[x]</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension.extension.value[x]</t>
   </si>
   <si>
     <t>Value of extension</t>
@@ -939,7 +997,7 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t>DiagnosticReport.performer.extension:author.extension:typeCode</t>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:typeCode</t>
   </si>
   <si>
     <t>typeCode</t>
@@ -948,60 +1006,60 @@
     <t>Type de participation</t>
   </si>
   <si>
-    <t>DiagnosticReport.performer.extension:author.extension:typeCode.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension:author.extension:typeCode.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension:author.extension:typeCode.url</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension:author.extension:typeCode.value[x]</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension:author.extension:actor</t>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:typeCode.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:typeCode.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:typeCode.url</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:typeCode.value[x]</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:actor</t>
   </si>
   <si>
     <t>actor</t>
   </si>
   <si>
-    <t>DiagnosticReport.performer.extension:author.extension:actor.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension:author.extension:actor.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension:author.extension:actor.url</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension:author.extension:actor.value[x]</t>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:actor.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:actor.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:actor.url</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.extension:actor.value[x]</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document)
 </t>
   </si>
   <si>
-    <t>DiagnosticReport.performer.extension:author.url</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension.url</t>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.url</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension.url</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension</t>
   </si>
   <si>
-    <t>DiagnosticReport.performer.extension:author.value[x]</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.performer.extension.value[x]</t>
+    <t>DiagnosticReport.resultsInterpreter.extension:author.value[x]</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.resultsInterpreter.extension.value[x]</t>
   </si>
   <si>
     <t>base64Binary
 booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
   </si>
   <si>
-    <t>DiagnosticReport.performer.reference</t>
+    <t>DiagnosticReport.resultsInterpreter.reference</t>
   </si>
   <si>
     <t>Literal reference, Relative, internal or absolute URL</t>
@@ -1020,7 +1078,7 @@
 </t>
   </si>
   <si>
-    <t>DiagnosticReport.performer.type</t>
+    <t>DiagnosticReport.resultsInterpreter.type</t>
   </si>
   <si>
     <t>Type the reference refers to (e.g. "Patient")</t>
@@ -1045,7 +1103,7 @@
     <t>Reference.type</t>
   </si>
   <si>
-    <t>DiagnosticReport.performer.identifier</t>
+    <t>DiagnosticReport.resultsInterpreter.identifier</t>
   </si>
   <si>
     <t>Logical reference, when literal reference is not known</t>
@@ -1066,7 +1124,7 @@
     <t>.identifier</t>
   </si>
   <si>
-    <t>DiagnosticReport.performer.display</t>
+    <t>DiagnosticReport.resultsInterpreter.display</t>
   </si>
   <si>
     <t>Text alternative for the resource</t>
@@ -1079,25 +1137,6 @@
   </si>
   <si>
     <t>Reference.display</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.resultsInterpreter</t>
-  </si>
-  <si>
-    <t>Analyzed by
-Reported by</t>
-  </si>
-  <si>
-    <t>Interpréteur de résultat primaire</t>
-  </si>
-  <si>
-    <t>The practitioner or organization that is responsible for the report's conclusions and interpretations.</t>
-  </si>
-  <si>
-    <t>Might not be the same entity that takes responsibility for the clinical report.</t>
-  </si>
-  <si>
-    <t>OBR-32, PRT-8 (where this PRT-4-Participation = "PI")</t>
   </si>
   <si>
     <t>DiagnosticReport.specimen</t>
@@ -1133,7 +1172,7 @@
 </t>
   </si>
   <si>
-    <t>Résultats</t>
+    <t>Résultats d'examen de biologie</t>
   </si>
   <si>
     <t>[Observations](http://hl7.org/fhir/R4/observation.html)  that are part of this diagnostic report.</t>
@@ -1181,7 +1220,7 @@
 </t>
   </si>
   <si>
-    <t>Key images associated with this report</t>
+    <t>Images clés associées à ce rapport</t>
   </si>
   <si>
     <t>A list of key images associated with this report. The images are generally created during the diagnostic process, and may be directly of the patient, or of treated specimens (i.e. slides of interest).</t>
@@ -1240,11 +1279,11 @@
     <t>DiagnosticReport.media.link</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Media|4.0.1)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-media-document)
 </t>
   </si>
   <si>
-    <t>Reference to the image source</t>
+    <t>Lien vers les images clés</t>
   </si>
   <si>
     <t>Reference to the image source.</t>
@@ -1282,6 +1321,9 @@
   </si>
   <si>
     <t>One or more codes that represent the summary conclusion (interpretation/impression) of the diagnostic report.</t>
+  </si>
+  <si>
+    <t>example</t>
   </si>
   <si>
     <t>Diagnosis codes provided as adjuncts to the report.</t>
@@ -1629,11 +1671,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN59"/>
+  <dimension ref="A1:AN61"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="61.234375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="47.4609375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="67.1484375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="53.375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="53.34375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -2821,7 +2863,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>147</v>
       </c>
@@ -2840,7 +2882,7 @@
         <v>79</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>80</v>
@@ -3101,7 +3143,7 @@
         <v>80</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>80</v>
+        <v>172</v>
       </c>
       <c r="T13" t="s" s="2">
         <v>80</v>
@@ -3116,13 +3158,13 @@
         <v>80</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Y13" t="s" s="2">
         <v>170</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>80</v>
@@ -3155,35 +3197,35 @@
         <v>102</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>90</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>91</v>
@@ -3195,16 +3237,16 @@
         <v>91</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3215,7 +3257,7 @@
         <v>80</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>80</v>
+        <v>185</v>
       </c>
       <c r="T14" t="s" s="2">
         <v>80</v>
@@ -3230,11 +3272,9 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>185</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
         <v>186</v>
       </c>
@@ -3242,19 +3282,17 @@
         <v>80</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="AC14" s="2"/>
       <c r="AD14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>80</v>
+        <v>188</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3272,32 +3310,34 @@
         <v>80</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="C15" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="D15" t="s" s="2">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>90</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>91</v>
@@ -3309,15 +3349,17 @@
         <v>91</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>80</v>
@@ -3344,11 +3386,9 @@
       <c r="X15" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="Y15" t="s" s="2">
-        <v>194</v>
-      </c>
+      <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>80</v>
@@ -3366,13 +3406,13 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>80</v>
@@ -3381,28 +3421,28 @@
         <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>196</v>
+        <v>80</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>199</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3421,18 +3461,16 @@
         <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="N16" s="2"/>
-      <c r="O16" t="s" s="2">
-        <v>205</v>
-      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>80</v>
       </c>
@@ -3456,13 +3494,13 @@
         <v>80</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>80</v>
+        <v>201</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>80</v>
@@ -3480,10 +3518,10 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>90</v>
@@ -3495,32 +3533,32 @@
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>90</v>
@@ -3535,19 +3573,17 @@
         <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>215</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" t="s" s="2">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>80</v>
@@ -3596,7 +3632,7 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3611,32 +3647,32 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>90</v>
@@ -3651,19 +3687,19 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>80</v>
@@ -3712,7 +3748,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3727,38 +3763,38 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>231</v>
+        <v>226</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>80</v>
@@ -3767,19 +3803,19 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>80</v>
@@ -3828,7 +3864,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3843,38 +3879,38 @@
         <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>80</v>
+        <v>234</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>80</v>
@@ -3883,19 +3919,19 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="O20" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>80</v>
@@ -3944,13 +3980,13 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>80</v>
@@ -3959,56 +3995,60 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>249</v>
+        <v>80</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>80</v>
+        <v>249</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="O21" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="L21" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>80</v>
       </c>
@@ -4044,83 +4084,87 @@
         <v>80</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="AC21" s="2"/>
       <c r="AD21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>80</v>
+        <v>188</v>
       </c>
       <c r="AF21" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AL21" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AG21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>258</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>80</v>
+        <v>259</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="D22" t="s" s="2">
-        <v>80</v>
+        <v>249</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>136</v>
+        <v>262</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
       </c>
@@ -4156,19 +4200,19 @@
         <v>80</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>263</v>
+        <v>80</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>264</v>
+        <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4180,61 +4224,63 @@
         <v>80</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>80</v>
+        <v>256</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>80</v>
+        <v>257</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>80</v>
+        <v>258</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>80</v>
+        <v>259</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>80</v>
+        <v>265</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="N23" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="L23" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
+      <c r="O23" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>80</v>
       </c>
@@ -4282,7 +4328,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4294,27 +4340,27 @@
         <v>80</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>80</v>
+        <v>256</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>80</v>
+        <v>269</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>80</v>
+        <v>258</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>80</v>
+        <v>259</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4337,13 +4383,13 @@
         <v>80</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4394,7 +4440,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4415,7 +4461,7 @@
         <v>80</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>80</v>
@@ -4423,10 +4469,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4434,7 +4480,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>275</v>
+        <v>90</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>79</v>
@@ -4452,10 +4498,10 @@
         <v>136</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4494,19 +4540,19 @@
         <v>80</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>264</v>
+        <v>188</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4535,13 +4581,13 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="B26" t="s" s="2">
-        <v>274</v>
-      </c>
       <c r="C26" t="s" s="2">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>80</v>
@@ -4551,7 +4597,7 @@
         <v>90</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>80</v>
@@ -4563,13 +4609,13 @@
         <v>80</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>136</v>
+        <v>284</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>260</v>
+        <v>285</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>261</v>
+        <v>286</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4620,7 +4666,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4649,10 +4695,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4675,13 +4721,13 @@
         <v>80</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4732,7 +4778,7 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4753,7 +4799,7 @@
         <v>80</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>80</v>
@@ -4761,10 +4807,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4772,10 +4818,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>78</v>
+        <v>291</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>80</v>
@@ -4790,10 +4836,10 @@
         <v>136</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4832,19 +4878,19 @@
         <v>80</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>264</v>
+        <v>188</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4873,12 +4919,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="C29" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="D29" t="s" s="2">
         <v>80</v>
       </c>
@@ -4899,24 +4947,22 @@
         <v>80</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>277</v>
+        <v>80</v>
       </c>
       <c r="S29" t="s" s="2">
         <v>80</v>
@@ -4958,19 +5004,19 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>80</v>
@@ -4979,7 +5025,7 @@
         <v>80</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>80</v>
@@ -4987,10 +5033,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5013,13 +5059,13 @@
         <v>80</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>110</v>
+        <v>271</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>291</v>
+        <v>273</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5031,7 +5077,7 @@
         <v>80</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>292</v>
+        <v>80</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>80</v>
@@ -5046,11 +5092,13 @@
         <v>80</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="Y30" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z30" t="s" s="2">
-        <v>293</v>
+        <v>80</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>80</v>
@@ -5068,7 +5116,7 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5080,7 +5128,7 @@
         <v>80</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>80</v>
@@ -5089,7 +5137,7 @@
         <v>80</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>133</v>
+        <v>275</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>80</v>
@@ -5097,14 +5145,12 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="C31" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>80</v>
       </c>
@@ -5113,7 +5159,7 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>80</v>
@@ -5128,10 +5174,10 @@
         <v>136</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5170,19 +5216,19 @@
         <v>80</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>80</v>
+        <v>279</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>80</v>
+        <v>188</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5214,7 +5260,7 @@
         <v>298</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5222,7 +5268,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>90</v>
@@ -5237,22 +5283,24 @@
         <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>254</v>
+        <v>104</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>255</v>
+        <v>300</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>80</v>
+        <v>293</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>80</v>
@@ -5294,10 +5342,10 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>257</v>
+        <v>303</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>90</v>
@@ -5315,7 +5363,7 @@
         <v>80</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>258</v>
+        <v>133</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>80</v>
@@ -5323,10 +5371,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>281</v>
+        <v>305</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5337,7 +5385,7 @@
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>80</v>
@@ -5349,13 +5397,13 @@
         <v>80</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>260</v>
+        <v>306</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>261</v>
+        <v>307</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5367,7 +5415,7 @@
         <v>80</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>80</v>
+        <v>308</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>80</v>
@@ -5382,43 +5430,41 @@
         <v>80</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>80</v>
+        <v>309</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>263</v>
+        <v>80</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>264</v>
+        <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>265</v>
+        <v>310</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>80</v>
@@ -5427,7 +5473,7 @@
         <v>80</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>80</v>
@@ -5435,18 +5481,20 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="C34" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>312</v>
+      </c>
       <c r="D34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>90</v>
@@ -5461,24 +5509,22 @@
         <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>284</v>
+        <v>313</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>296</v>
+        <v>80</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>80</v>
@@ -5520,19 +5566,19 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>80</v>
@@ -5541,7 +5587,7 @@
         <v>80</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>80</v>
@@ -5549,10 +5595,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5575,13 +5621,13 @@
         <v>80</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>180</v>
+        <v>271</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>291</v>
+        <v>273</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5632,7 +5678,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5644,7 +5690,7 @@
         <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>80</v>
@@ -5653,7 +5699,7 @@
         <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>133</v>
+        <v>275</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>80</v>
@@ -5661,23 +5707,21 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>303</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>80</v>
@@ -5692,10 +5736,10 @@
         <v>136</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5734,19 +5778,19 @@
         <v>80</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>80</v>
+        <v>279</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>80</v>
+        <v>188</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5775,10 +5819,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5786,7 +5830,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>90</v>
@@ -5801,22 +5845,24 @@
         <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>254</v>
+        <v>104</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>255</v>
+        <v>300</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>80</v>
+        <v>312</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>80</v>
@@ -5858,10 +5904,10 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>257</v>
+        <v>303</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>90</v>
@@ -5879,7 +5925,7 @@
         <v>80</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>258</v>
+        <v>133</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>80</v>
@@ -5887,10 +5933,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="B38" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5901,7 +5947,7 @@
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>80</v>
@@ -5913,13 +5959,13 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>136</v>
+        <v>181</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>260</v>
+        <v>306</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>261</v>
+        <v>307</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5958,31 +6004,31 @@
         <v>80</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>262</v>
+        <v>80</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>263</v>
+        <v>80</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>264</v>
+        <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>265</v>
+        <v>310</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>80</v>
@@ -5991,7 +6037,7 @@
         <v>80</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>80</v>
@@ -5999,12 +6045,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="C39" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="D39" t="s" s="2">
         <v>80</v>
       </c>
@@ -6025,24 +6073,22 @@
         <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>303</v>
+        <v>80</v>
       </c>
       <c r="S39" t="s" s="2">
         <v>80</v>
@@ -6084,19 +6130,19 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>80</v>
@@ -6105,7 +6151,7 @@
         <v>80</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>80</v>
@@ -6113,10 +6159,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6139,13 +6185,13 @@
         <v>80</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>308</v>
+        <v>271</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>291</v>
+        <v>273</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6196,7 +6242,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6208,7 +6254,7 @@
         <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>80</v>
@@ -6217,7 +6263,7 @@
         <v>80</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>133</v>
+        <v>275</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>80</v>
@@ -6225,10 +6271,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>310</v>
+        <v>297</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6236,10 +6282,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>80</v>
@@ -6251,24 +6297,22 @@
         <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>311</v>
+        <v>80</v>
       </c>
       <c r="S41" t="s" s="2">
         <v>80</v>
@@ -6298,31 +6342,31 @@
         <v>80</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>80</v>
+        <v>279</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>80</v>
+        <v>188</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>80</v>
@@ -6331,7 +6375,7 @@
         <v>80</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>80</v>
@@ -6339,10 +6383,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6350,10 +6394,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>80</v>
@@ -6365,22 +6409,24 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>314</v>
+        <v>104</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>80</v>
+        <v>319</v>
       </c>
       <c r="S42" t="s" s="2">
         <v>80</v>
@@ -6422,10 +6468,10 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>90</v>
@@ -6434,7 +6480,7 @@
         <v>80</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>80</v>
@@ -6451,10 +6497,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6474,20 +6520,18 @@
         <v>80</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>254</v>
+        <v>324</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>318</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>80</v>
@@ -6536,7 +6580,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6545,7 +6589,7 @@
         <v>90</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>320</v>
+        <v>80</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>102</v>
@@ -6565,10 +6609,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6576,7 +6620,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>90</v>
@@ -6588,19 +6632,19 @@
         <v>80</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>322</v>
+        <v>300</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>323</v>
+        <v>301</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>324</v>
+        <v>302</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6608,7 +6652,7 @@
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>80</v>
+        <v>327</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>80</v>
@@ -6626,13 +6670,13 @@
         <v>80</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>325</v>
+        <v>80</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>326</v>
+        <v>80</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>327</v>
+        <v>80</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>80</v>
@@ -6650,10 +6694,10 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>328</v>
+        <v>303</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>90</v>
@@ -6662,7 +6706,7 @@
         <v>80</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>80</v>
@@ -6679,7 +6723,7 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>329</v>
@@ -6693,7 +6737,7 @@
         <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>80</v>
@@ -6702,20 +6746,18 @@
         <v>80</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>149</v>
+        <v>330</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>330</v>
+        <v>306</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>332</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>80</v>
@@ -6764,7 +6806,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>333</v>
+        <v>310</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6785,7 +6827,7 @@
         <v>80</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>334</v>
+        <v>133</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>80</v>
@@ -6793,10 +6835,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6819,16 +6861,16 @@
         <v>91</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6878,7 +6920,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6887,7 +6929,7 @@
         <v>90</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>80</v>
+        <v>336</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>102</v>
@@ -6905,26 +6947,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>341</v>
+        <v>80</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>80</v>
@@ -6933,20 +6975,18 @@
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>308</v>
+        <v>104</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>80</v>
       </c>
@@ -6970,13 +7010,13 @@
         <v>80</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>80</v>
+        <v>341</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>80</v>
+        <v>342</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>80</v>
+        <v>343</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>80</v>
@@ -6994,13 +7034,13 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>80</v>
@@ -7009,24 +7049,24 @@
         <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>249</v>
+        <v>80</v>
       </c>
       <c r="AL47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="48" hidden="true">
+      <c r="A48" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="AM47" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s" s="2">
-        <v>346</v>
-      </c>
       <c r="B48" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7037,32 +7077,30 @@
         <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J48" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J48" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K48" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="M48" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>351</v>
-      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>80</v>
       </c>
@@ -7110,13 +7148,13 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>80</v>
@@ -7128,57 +7166,55 @@
         <v>80</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>352</v>
+        <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>208</v>
+        <v>350</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>354</v>
+        <v>80</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J49" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K49" t="s" s="2">
-        <v>355</v>
+        <v>271</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>359</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>80</v>
       </c>
@@ -7226,13 +7262,13 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>80</v>
@@ -7244,21 +7280,21 @@
         <v>80</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>360</v>
+        <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>361</v>
+        <v>133</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7272,7 +7308,7 @@
         <v>79</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>80</v>
@@ -7281,18 +7317,20 @@
         <v>80</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
       </c>
@@ -7340,7 +7378,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7358,54 +7396,56 @@
         <v>80</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>80</v>
+        <v>362</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>367</v>
+        <v>214</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="O51" t="s" s="2">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -7454,7 +7494,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7472,10 +7512,10 @@
         <v>80</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>80</v>
@@ -7483,10 +7523,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7497,7 +7537,7 @@
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>80</v>
@@ -7509,15 +7549,17 @@
         <v>80</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>254</v>
+        <v>373</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>255</v>
+        <v>374</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -7566,19 +7608,19 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>257</v>
+        <v>372</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>80</v>
@@ -7587,22 +7629,22 @@
         <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>258</v>
+        <v>377</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>135</v>
+        <v>379</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7612,27 +7654,27 @@
         <v>79</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>136</v>
+        <v>380</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>137</v>
+        <v>381</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>382</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>80</v>
       </c>
@@ -7680,7 +7722,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>265</v>
+        <v>378</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7692,16 +7734,16 @@
         <v>80</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>80</v>
+        <v>384</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>258</v>
+        <v>371</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>80</v>
@@ -7709,46 +7751,42 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>379</v>
+        <v>80</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>136</v>
+        <v>271</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>380</v>
+        <v>272</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>80</v>
       </c>
@@ -7796,19 +7834,19 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>382</v>
+        <v>274</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>141</v>
+        <v>80</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>80</v>
@@ -7817,7 +7855,7 @@
         <v>80</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>133</v>
+        <v>275</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>80</v>
@@ -7825,21 +7863,21 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>80</v>
@@ -7851,20 +7889,18 @@
         <v>80</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>254</v>
+        <v>136</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>384</v>
+        <v>137</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>387</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>80</v>
       </c>
@@ -7912,19 +7948,19 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>383</v>
+        <v>281</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>80</v>
@@ -7933,7 +7969,7 @@
         <v>80</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>388</v>
+        <v>275</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>80</v>
@@ -7941,42 +7977,46 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>80</v>
+        <v>389</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J56" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="M56" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+      <c r="N56" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>80</v>
       </c>
@@ -8024,19 +8064,19 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>80</v>
@@ -8045,22 +8085,22 @@
         <v>80</v>
       </c>
       <c r="AM56" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AN56" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s" s="2">
-        <v>394</v>
-      </c>
       <c r="B57" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>395</v>
+        <v>80</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8070,7 +8110,7 @@
         <v>90</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>80</v>
@@ -8079,17 +8119,19 @@
         <v>80</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="N57" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="O57" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>80</v>
@@ -8138,7 +8180,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8156,21 +8198,21 @@
         <v>80</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AM57" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="58" hidden="true">
-      <c r="A58" t="s" s="2">
-        <v>401</v>
-      </c>
       <c r="B58" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8178,28 +8220,28 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>180</v>
+        <v>400</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8226,13 +8268,13 @@
         <v>80</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>184</v>
+        <v>80</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>404</v>
+        <v>80</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>405</v>
+        <v>80</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>80</v>
@@ -8250,13 +8292,13 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>80</v>
@@ -8268,10 +8310,10 @@
         <v>80</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>399</v>
+        <v>80</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>80</v>
@@ -8279,18 +8321,18 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>80</v>
+        <v>405</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>90</v>
@@ -8305,19 +8347,17 @@
         <v>80</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>80</v>
@@ -8366,13 +8406,13 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>80</v>
@@ -8384,17 +8424,245 @@
         <v>80</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="AM59" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="AN59" t="s" s="2">
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="P61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN59">
+  <autoFilter ref="A1:AN61">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8404,7 +8672,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI58">
+  <conditionalFormatting sqref="A2:AI60">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-diagnostic-report-bio-chapter-document.xlsx
+++ b/main/ig/StructureDefinition-fr-diagnostic-report-bio-chapter-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T15:31:02+00:00</t>
+    <t>2026-06-16T14:27:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-diagnostic-report-bio-chapter-document.xlsx
+++ b/main/ig/StructureDefinition-fr-diagnostic-report-bio-chapter-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:27:29+00:00</t>
+    <t>2026-06-18T14:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-diagnostic-report-bio-chapter-document.xlsx
+++ b/main/ig/StructureDefinition-fr-diagnostic-report-bio-chapter-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:40:49+00:00</t>
+    <t>2026-06-22T09:35:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
